--- a/Preparation-info.xlsx
+++ b/Preparation-info.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Nodejs-live-Class\Class-Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0742762D-7B27-43C3-99DA-13F2022E5C60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64454BE-ECC0-49D9-B8CD-532015F3E421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Day-1" sheetId="1" r:id="rId1"/>
     <sheet name="GS" sheetId="2" r:id="rId2"/>
+    <sheet name="Useful command" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
   <si>
     <t>Date of Prepration</t>
   </si>
@@ -131,13 +132,371 @@
   </si>
   <si>
     <t>How to working  GIT Desktop Application is working</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"C:\Program Files\Git\cmd\git.exe" --version</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+  </si>
+  <si>
+    <t>git version 2.55.0.windows.2</t>
+  </si>
+  <si>
+    <t>git --version</t>
+  </si>
+  <si>
+    <t>Git from the command line and also from 3rd-party software</t>
+  </si>
+  <si>
+    <t>3. Add Git to PATH</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Press </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Win + S</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and search for </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Environment Variables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">2. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Edit the system environment variables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Environment Variables...</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">4. Under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>System variables</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, select </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Path</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> → </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Edit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">5. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>New</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and add:</t>
+    </r>
+  </si>
+  <si>
+    <t>C:\Program Files\Git\cmd</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">(or the folder where </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>git.exe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is located)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">6. Click </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> on all windows.</t>
+    </r>
+  </si>
+  <si>
+    <t>7. Close and reopen PowerShell or VS Code.</t>
+  </si>
+  <si>
+    <t>git</t>
+  </si>
+  <si>
+    <t>These are common Git commands used in various situations:</t>
+  </si>
+  <si>
+    <t>&gt; git config --global user.name "kumar B"</t>
+  </si>
+  <si>
+    <t>&gt; git config --global user.email "kumaraswamy.b.edu@gmail.com"</t>
+  </si>
+  <si>
+    <t>step 1: Verify your configuration</t>
+  </si>
+  <si>
+    <t>git config --global --list</t>
+  </si>
+  <si>
+    <t>You should see something like:
+user.name=kumar B
+user.email=kumaraswamy.b.edu@gmail.com</t>
+  </si>
+  <si>
+    <t>Step 2: Check the repository status</t>
+  </si>
+  <si>
+    <t>git status</t>
+  </si>
+  <si>
+    <t>Step 3: Add and commit your files</t>
+  </si>
+  <si>
+    <t>git add .
+git commit -m "Initial commit</t>
+  </si>
+  <si>
+    <t>If the commit is successful, continue.</t>
+  </si>
+  <si>
+    <t>Step 4: Check your branch</t>
+  </si>
+  <si>
+    <t>git branch</t>
+  </si>
+  <si>
+    <t>Check the existing remote</t>
+  </si>
+  <si>
+    <t>git remote -v</t>
+  </si>
+  <si>
+    <t>If it shows:</t>
+  </si>
+  <si>
+    <t>origin  https://github.com/kumaraswamybedu/Nodejs-live-Class.git (fetch)
+origin  https://github.com/kumaraswamybedu/Nodejs-live-Class.git (push)</t>
+  </si>
+  <si>
+    <t>* master</t>
+  </si>
+  <si>
+    <t>rename it:</t>
+  </si>
+  <si>
+    <t>git branch -M main</t>
+  </si>
+  <si>
+    <t>Step 5: Push to GitHub</t>
+  </si>
+  <si>
+    <t>git push -u origin main</t>
+  </si>
+  <si>
+    <t>If git commit still gives the email error</t>
+  </si>
+  <si>
+    <t>Sometimes the terminal needs to be restarted to pick up the configuration.</t>
+  </si>
+  <si>
+    <t>11. what is module system in nodejs</t>
+  </si>
+  <si>
+    <t>12.what is module ?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +515,52 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -188,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -205,6 +610,27 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,8 +911,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16.21875" style="4" customWidth="1"/>
@@ -498,7 +924,7 @@
     <col min="8" max="8" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
@@ -524,7 +950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -547,12 +973,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="G3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="5"/>
       <c r="B4" s="6"/>
       <c r="C4" s="5"/>
@@ -562,7 +988,7 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -579,7 +1005,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8">
       <c r="D6" s="4" t="s">
         <v>19</v>
       </c>
@@ -590,22 +1016,22 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8">
       <c r="D7" s="4" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8">
       <c r="D9" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="D10" s="4" t="s">
         <v>30</v>
       </c>
@@ -613,24 +1039,34 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="D11" s="4" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="D12" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="D13" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="D14" s="4" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="D15" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="D16" s="4" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -640,14 +1076,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7033126A-25FF-483B-9641-E9CA0D537DE8}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="40.77734375" customWidth="1"/>
+    <col min="1" max="1" width="55.88671875" customWidth="1"/>
     <col min="2" max="2" width="113.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="21" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2" ht="21">
       <c r="A1" s="7" t="s">
         <v>31</v>
       </c>
@@ -655,12 +1091,234 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
         <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11D54DDB-35CC-48D5-8F0D-A2C03014DB25}">
+  <dimension ref="A2:B45"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="81.44140625" customWidth="1"/>
+    <col min="2" max="2" width="50.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:2" ht="28.8">
+      <c r="A2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="18">
+      <c r="A5" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="11"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="11" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="10"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="15" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="11"/>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="16" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="57.6">
+      <c r="A25" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="28.8">
+      <c r="A29" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="14"/>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="28.8">
+      <c r="A45" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/Preparation-info.xlsx
+++ b/Preparation-info.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\Nodejs-live-Class\Class-Notes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64454BE-ECC0-49D9-B8CD-532015F3E421}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00532C21-06E4-4C98-9961-3A9CD75BB2FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Day-1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="79">
   <si>
     <t>Date of Prepration</t>
   </si>
@@ -490,6 +490,15 @@
   </si>
   <si>
     <t>12.what is module ?</t>
+  </si>
+  <si>
+    <t>13.Module vs module systems</t>
+  </si>
+  <si>
+    <t>14.How many types are avalable in module system in js</t>
+  </si>
+  <si>
+    <t>GitHub Copilot, IntelliSens  (unable this in VS code)</t>
   </si>
 </sst>
 </file>
@@ -911,13 +920,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="16.21875" style="4" customWidth="1"/>
     <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.88671875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="47.44140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="43.109375" customWidth="1"/>
     <col min="6" max="6" width="19.77734375" customWidth="1"/>
     <col min="7" max="7" width="55" customWidth="1"/>
@@ -1069,6 +1078,21 @@
         <v>75</v>
       </c>
     </row>
+    <row r="17" spans="4:4">
+      <c r="D17" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="4:4">
+      <c r="D18" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4">
+      <c r="D19" s="4">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1076,7 +1100,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7033126A-25FF-483B-9641-E9CA0D537DE8}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="55.88671875" customWidth="1"/>
@@ -1102,6 +1126,11 @@
     <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
